--- a/Defense_Platform_Business_Plan_Financial_V2.xlsx
+++ b/Defense_Platform_Business_Plan_Financial_V2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WINCODE\NDAD-Business-Plan\NDAD-Business-Plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\GitHub\NDAD-Business-Plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CD2659-DCAF-4962-891F-20DEB44A9C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244461C9-5539-4807-8403-99CCAB28AADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="817" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="817" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -4386,25 +4386,23 @@
     <xf numFmtId="167" fontId="12" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4417,17 +4415,20 @@
     <xf numFmtId="165" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4440,6 +4441,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4456,16 +4460,12 @@
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7160,108 +7160,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="115" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="115"/>
-      <c r="D2" s="115"/>
-      <c r="E2" s="115"/>
-      <c r="F2" s="115"/>
+      <c r="B2" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="E2" s="120"/>
+      <c r="F2" s="120"/>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="116"/>
-      <c r="D3" s="116"/>
-      <c r="E3" s="116"/>
-      <c r="F3" s="116"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
     </row>
     <row r="5" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="117" t="s">
+      <c r="C5" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
     </row>
     <row r="6" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="117" t="s">
+      <c r="C6" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="F6" s="117"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
     </row>
     <row r="7" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="117" t="s">
+      <c r="C7" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="F7" s="117"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
     </row>
     <row r="8" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="F8" s="117"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
     </row>
     <row r="9" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="117" t="s">
+      <c r="C9" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="F9" s="117"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
     </row>
     <row r="10" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="F10" s="117"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="119"/>
     </row>
     <row r="11" spans="2:6" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="117" t="s">
+      <c r="C11" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="F11" s="117"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="119"/>
     </row>
     <row r="13" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
     </row>
     <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
@@ -7384,16 +7384,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7417,55 +7417,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>470</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>472</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -7506,20 +7506,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="136" t="s">
         <v>474</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -7789,20 +7789,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="134" t="s">
+      <c r="B14" s="136" t="s">
         <v>482</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -8072,20 +8072,20 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="136" t="s">
         <v>483</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -8355,21 +8355,21 @@
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="117" t="s">
         <v>484</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -8674,55 +8674,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>489</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>490</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -8763,20 +8763,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="136" t="s">
         <v>491</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -9046,20 +9046,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="134" t="s">
+      <c r="B14" s="136" t="s">
         <v>492</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -9329,20 +9329,20 @@
       </c>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="136" t="s">
         <v>493</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -9612,20 +9612,20 @@
       </c>
     </row>
     <row r="30" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="136" t="s">
         <v>494</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="134"/>
-      <c r="F30" s="134"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="134"/>
-      <c r="J30" s="134"/>
-      <c r="K30" s="134"/>
-      <c r="L30" s="134"/>
-      <c r="M30" s="134"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="136"/>
+      <c r="E30" s="136"/>
+      <c r="F30" s="136"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="136"/>
+      <c r="I30" s="136"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="136"/>
+      <c r="L30" s="136"/>
+      <c r="M30" s="136"/>
     </row>
     <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="68" t="s">
@@ -9895,21 +9895,21 @@
       </c>
     </row>
     <row r="38" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="118" t="s">
+      <c r="B38" s="117" t="s">
         <v>495</v>
       </c>
-      <c r="C38" s="118"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="118"/>
-      <c r="G38" s="118"/>
-      <c r="H38" s="118"/>
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-      <c r="K38" s="118"/>
-      <c r="L38" s="118"/>
-      <c r="M38" s="118"/>
-      <c r="N38" s="118"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="117"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="117"/>
+      <c r="H38" s="117"/>
+      <c r="I38" s="117"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="117"/>
+      <c r="L38" s="117"/>
+      <c r="M38" s="117"/>
+      <c r="N38" s="117"/>
     </row>
     <row r="39" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="42" t="s">
@@ -10319,55 +10319,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>513</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>514</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -10408,20 +10408,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="136" t="s">
+      <c r="B6" s="138" t="s">
         <v>515</v>
       </c>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="138"/>
+      <c r="F6" s="138"/>
+      <c r="G6" s="138"/>
+      <c r="H6" s="138"/>
+      <c r="I6" s="138"/>
+      <c r="J6" s="138"/>
+      <c r="K6" s="138"/>
+      <c r="L6" s="138"/>
+      <c r="M6" s="138"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -10691,20 +10691,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="138" t="s">
         <v>516</v>
       </c>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="136"/>
-      <c r="I14" s="136"/>
-      <c r="J14" s="136"/>
-      <c r="K14" s="136"/>
-      <c r="L14" s="136"/>
-      <c r="M14" s="136"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="138"/>
+      <c r="H14" s="138"/>
+      <c r="I14" s="138"/>
+      <c r="J14" s="138"/>
+      <c r="K14" s="138"/>
+      <c r="L14" s="138"/>
+      <c r="M14" s="138"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -10974,20 +10974,20 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="138" t="s">
         <v>517</v>
       </c>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="136"/>
-      <c r="F22" s="136"/>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="136"/>
-      <c r="J22" s="136"/>
-      <c r="K22" s="136"/>
-      <c r="L22" s="136"/>
-      <c r="M22" s="136"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="138"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="138"/>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="138"/>
+      <c r="M22" s="138"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -11257,21 +11257,21 @@
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="117" t="s">
         <v>518</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -11576,55 +11576,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>519</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>520</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -11665,20 +11665,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="136" t="s">
         <v>521</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
-      <c r="K6" s="134"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="136"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="136"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -11948,20 +11948,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="134" t="s">
+      <c r="B14" s="136" t="s">
         <v>522</v>
       </c>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="E14" s="134"/>
-      <c r="F14" s="134"/>
-      <c r="G14" s="134"/>
-      <c r="H14" s="134"/>
-      <c r="I14" s="134"/>
-      <c r="J14" s="134"/>
-      <c r="K14" s="134"/>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="136"/>
+      <c r="I14" s="136"/>
+      <c r="J14" s="136"/>
+      <c r="K14" s="136"/>
+      <c r="L14" s="136"/>
+      <c r="M14" s="136"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -12231,20 +12231,20 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="136" t="s">
         <v>523</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
-      <c r="M22" s="134"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="136"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="136"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="136"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -12514,21 +12514,21 @@
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="117" t="s">
         <v>524</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -12833,55 +12833,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>525</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>526</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -12922,20 +12922,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="139" t="s">
         <v>527</v>
       </c>
-      <c r="C6" s="137"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
+      <c r="C6" s="139"/>
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="139"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="139"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -13205,20 +13205,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="137" t="s">
+      <c r="B14" s="139" t="s">
         <v>528</v>
       </c>
-      <c r="C14" s="137"/>
-      <c r="D14" s="137"/>
-      <c r="E14" s="137"/>
-      <c r="F14" s="137"/>
-      <c r="G14" s="137"/>
-      <c r="H14" s="137"/>
-      <c r="I14" s="137"/>
-      <c r="J14" s="137"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="137"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="139"/>
+      <c r="F14" s="139"/>
+      <c r="G14" s="139"/>
+      <c r="H14" s="139"/>
+      <c r="I14" s="139"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="139"/>
+      <c r="L14" s="139"/>
+      <c r="M14" s="139"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -13488,20 +13488,20 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="137" t="s">
+      <c r="B22" s="139" t="s">
         <v>529</v>
       </c>
-      <c r="C22" s="137"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
-      <c r="G22" s="137"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="137"/>
-      <c r="J22" s="137"/>
-      <c r="K22" s="137"/>
-      <c r="L22" s="137"/>
-      <c r="M22" s="137"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="139"/>
+      <c r="I22" s="139"/>
+      <c r="J22" s="139"/>
+      <c r="K22" s="139"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="139"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -13771,21 +13771,21 @@
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="117" t="s">
         <v>530</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -14090,55 +14090,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>469</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>531</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="119" t="s">
         <v>532</v>
       </c>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
+      <c r="L3" s="119"/>
+      <c r="M3" s="119"/>
     </row>
     <row r="5" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="10" t="s">
@@ -14179,20 +14179,20 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="138" t="s">
+      <c r="B6" s="140" t="s">
         <v>533</v>
       </c>
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="138"/>
-      <c r="H6" s="138"/>
-      <c r="I6" s="138"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138"/>
-      <c r="M6" s="138"/>
+      <c r="C6" s="140"/>
+      <c r="D6" s="140"/>
+      <c r="E6" s="140"/>
+      <c r="F6" s="140"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
     </row>
     <row r="7" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
@@ -14462,20 +14462,20 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="138" t="s">
+      <c r="B14" s="140" t="s">
         <v>534</v>
       </c>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="138"/>
-      <c r="J14" s="138"/>
-      <c r="K14" s="138"/>
-      <c r="L14" s="138"/>
-      <c r="M14" s="138"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="140"/>
+      <c r="H14" s="140"/>
+      <c r="I14" s="140"/>
+      <c r="J14" s="140"/>
+      <c r="K14" s="140"/>
+      <c r="L14" s="140"/>
+      <c r="M14" s="140"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68" t="s">
@@ -14745,20 +14745,20 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="140" t="s">
         <v>535</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
-      <c r="H22" s="138"/>
-      <c r="I22" s="138"/>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="138"/>
-      <c r="M22" s="138"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="140"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="68" t="s">
@@ -15028,21 +15028,21 @@
       </c>
     </row>
     <row r="30" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="118" t="s">
+      <c r="B30" s="117" t="s">
         <v>536</v>
       </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="118"/>
-      <c r="J30" s="118"/>
-      <c r="K30" s="118"/>
-      <c r="L30" s="118"/>
-      <c r="M30" s="118"/>
-      <c r="N30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="117"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="117"/>
+      <c r="G30" s="117"/>
+      <c r="H30" s="117"/>
+      <c r="I30" s="117"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="117"/>
+      <c r="L30" s="117"/>
+      <c r="M30" s="117"/>
+      <c r="N30" s="117"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -15346,37 +15346,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="137" t="s">
         <v>537</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
     </row>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>538</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="3" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -15425,21 +15425,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>542</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="49" t="s">
@@ -15776,21 +15776,21 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>545</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="43" t="s">
@@ -16063,21 +16063,21 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="117" t="s">
         <v>552</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="49" t="s">
@@ -16413,21 +16413,21 @@
       </c>
     </row>
     <row r="31" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="118" t="s">
+      <c r="B31" s="117" t="s">
         <v>555</v>
       </c>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="118"/>
-      <c r="N31" s="118"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="117"/>
+      <c r="N31" s="117"/>
     </row>
     <row r="32" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="42" t="s">
@@ -16559,36 +16559,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>559</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="3" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="116" t="s">
         <v>560</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -16629,20 +16629,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>562</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
@@ -16879,20 +16879,20 @@
       </c>
     </row>
     <row r="12" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="118" t="s">
+      <c r="B12" s="117" t="s">
         <v>569</v>
       </c>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
+      <c r="K12" s="117"/>
+      <c r="L12" s="117"/>
+      <c r="M12" s="117"/>
     </row>
     <row r="13" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="68" t="s">
@@ -17129,20 +17129,20 @@
       </c>
     </row>
     <row r="19" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="117" t="s">
         <v>576</v>
       </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="117"/>
     </row>
     <row r="20" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="68" t="s">
@@ -17400,20 +17400,20 @@
       </c>
     </row>
     <row r="28" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="117" t="s">
         <v>584</v>
       </c>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="118"/>
-      <c r="G28" s="118"/>
-      <c r="H28" s="118"/>
-      <c r="I28" s="118"/>
-      <c r="J28" s="118"/>
-      <c r="K28" s="118"/>
-      <c r="L28" s="118"/>
-      <c r="M28" s="118"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="117"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="117"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="117"/>
+      <c r="L28" s="117"/>
+      <c r="M28" s="117"/>
     </row>
     <row r="29" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="68" t="s">
@@ -17731,20 +17731,20 @@
       </c>
     </row>
     <row r="37" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="118" t="s">
+      <c r="B37" s="117" t="s">
         <v>592</v>
       </c>
-      <c r="C37" s="118"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-      <c r="K37" s="118"/>
-      <c r="L37" s="118"/>
-      <c r="M37" s="118"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="117"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="117"/>
+      <c r="G37" s="117"/>
+      <c r="H37" s="117"/>
+      <c r="I37" s="117"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="117"/>
+      <c r="L37" s="117"/>
+      <c r="M37" s="117"/>
     </row>
     <row r="38" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="12" t="s">
@@ -17882,20 +17882,20 @@
       </c>
     </row>
     <row r="42" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="118" t="s">
+      <c r="B42" s="117" t="s">
         <v>596</v>
       </c>
-      <c r="C42" s="118"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="118"/>
-      <c r="H42" s="118"/>
-      <c r="I42" s="118"/>
-      <c r="J42" s="118"/>
-      <c r="K42" s="118"/>
-      <c r="L42" s="118"/>
-      <c r="M42" s="118"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="117"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="117"/>
+      <c r="G42" s="117"/>
+      <c r="H42" s="117"/>
+      <c r="I42" s="117"/>
+      <c r="J42" s="117"/>
+      <c r="K42" s="117"/>
+      <c r="L42" s="117"/>
+      <c r="M42" s="117"/>
     </row>
     <row r="43" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="68" t="s">
@@ -18213,20 +18213,20 @@
       </c>
     </row>
     <row r="51" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="118" t="s">
+      <c r="B51" s="117" t="s">
         <v>602</v>
       </c>
-      <c r="C51" s="118"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="118"/>
-      <c r="G51" s="118"/>
-      <c r="H51" s="118"/>
-      <c r="I51" s="118"/>
-      <c r="J51" s="118"/>
-      <c r="K51" s="118"/>
-      <c r="L51" s="118"/>
-      <c r="M51" s="118"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="117"/>
+      <c r="I51" s="117"/>
+      <c r="J51" s="117"/>
+      <c r="K51" s="117"/>
+      <c r="L51" s="117"/>
+      <c r="M51" s="117"/>
     </row>
     <row r="52" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="68" t="s">
@@ -18499,20 +18499,20 @@
       </c>
     </row>
     <row r="59" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="118" t="s">
+      <c r="B59" s="117" t="s">
         <v>609</v>
       </c>
-      <c r="C59" s="118"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="118"/>
-      <c r="G59" s="118"/>
-      <c r="H59" s="118"/>
-      <c r="I59" s="118"/>
-      <c r="J59" s="118"/>
-      <c r="K59" s="118"/>
-      <c r="L59" s="118"/>
-      <c r="M59" s="118"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="117"/>
+      <c r="E59" s="117"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="117"/>
+      <c r="L59" s="117"/>
+      <c r="M59" s="117"/>
     </row>
     <row r="60" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="68" t="s">
@@ -18740,132 +18740,132 @@
       </c>
     </row>
     <row r="66" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="118" t="s">
+      <c r="B66" s="117" t="s">
         <v>615</v>
       </c>
-      <c r="C66" s="118"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="118"/>
-      <c r="G66" s="118"/>
-      <c r="H66" s="118"/>
-      <c r="I66" s="118"/>
-      <c r="J66" s="118"/>
-      <c r="K66" s="118"/>
-      <c r="L66" s="118"/>
-      <c r="M66" s="118"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="117"/>
+      <c r="E66" s="117"/>
+      <c r="F66" s="117"/>
+      <c r="G66" s="117"/>
+      <c r="H66" s="117"/>
+      <c r="I66" s="117"/>
+      <c r="J66" s="117"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="117"/>
+      <c r="M66" s="117"/>
     </row>
     <row r="67" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="139" t="s">
+      <c r="B67" s="116" t="s">
         <v>616</v>
       </c>
-      <c r="C67" s="139"/>
-      <c r="D67" s="139"/>
-      <c r="E67" s="139"/>
-      <c r="F67" s="139"/>
-      <c r="G67" s="139"/>
-      <c r="H67" s="139"/>
-      <c r="I67" s="139"/>
-      <c r="J67" s="139"/>
-      <c r="K67" s="139"/>
-      <c r="L67" s="139"/>
-      <c r="M67" s="139"/>
+      <c r="C67" s="116"/>
+      <c r="D67" s="116"/>
+      <c r="E67" s="116"/>
+      <c r="F67" s="116"/>
+      <c r="G67" s="116"/>
+      <c r="H67" s="116"/>
+      <c r="I67" s="116"/>
+      <c r="J67" s="116"/>
+      <c r="K67" s="116"/>
+      <c r="L67" s="116"/>
+      <c r="M67" s="116"/>
     </row>
     <row r="68" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="139" t="s">
+      <c r="B68" s="116" t="s">
         <v>617</v>
       </c>
-      <c r="C68" s="139"/>
-      <c r="D68" s="139"/>
-      <c r="E68" s="139"/>
-      <c r="F68" s="139"/>
-      <c r="G68" s="139"/>
-      <c r="H68" s="139"/>
-      <c r="I68" s="139"/>
-      <c r="J68" s="139"/>
-      <c r="K68" s="139"/>
-      <c r="L68" s="139"/>
-      <c r="M68" s="139"/>
+      <c r="C68" s="116"/>
+      <c r="D68" s="116"/>
+      <c r="E68" s="116"/>
+      <c r="F68" s="116"/>
+      <c r="G68" s="116"/>
+      <c r="H68" s="116"/>
+      <c r="I68" s="116"/>
+      <c r="J68" s="116"/>
+      <c r="K68" s="116"/>
+      <c r="L68" s="116"/>
+      <c r="M68" s="116"/>
     </row>
     <row r="69" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="139" t="s">
+      <c r="B69" s="116" t="s">
         <v>618</v>
       </c>
-      <c r="C69" s="139"/>
-      <c r="D69" s="139"/>
-      <c r="E69" s="139"/>
-      <c r="F69" s="139"/>
-      <c r="G69" s="139"/>
-      <c r="H69" s="139"/>
-      <c r="I69" s="139"/>
-      <c r="J69" s="139"/>
-      <c r="K69" s="139"/>
-      <c r="L69" s="139"/>
-      <c r="M69" s="139"/>
+      <c r="C69" s="116"/>
+      <c r="D69" s="116"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="116"/>
+      <c r="G69" s="116"/>
+      <c r="H69" s="116"/>
+      <c r="I69" s="116"/>
+      <c r="J69" s="116"/>
+      <c r="K69" s="116"/>
+      <c r="L69" s="116"/>
+      <c r="M69" s="116"/>
     </row>
     <row r="70" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="139" t="s">
+      <c r="B70" s="116" t="s">
         <v>619</v>
       </c>
-      <c r="C70" s="139"/>
-      <c r="D70" s="139"/>
-      <c r="E70" s="139"/>
-      <c r="F70" s="139"/>
-      <c r="G70" s="139"/>
-      <c r="H70" s="139"/>
-      <c r="I70" s="139"/>
-      <c r="J70" s="139"/>
-      <c r="K70" s="139"/>
-      <c r="L70" s="139"/>
-      <c r="M70" s="139"/>
+      <c r="C70" s="116"/>
+      <c r="D70" s="116"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="116"/>
+      <c r="G70" s="116"/>
+      <c r="H70" s="116"/>
+      <c r="I70" s="116"/>
+      <c r="J70" s="116"/>
+      <c r="K70" s="116"/>
+      <c r="L70" s="116"/>
+      <c r="M70" s="116"/>
     </row>
     <row r="71" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="139" t="s">
+      <c r="B71" s="116" t="s">
         <v>620</v>
       </c>
-      <c r="C71" s="139"/>
-      <c r="D71" s="139"/>
-      <c r="E71" s="139"/>
-      <c r="F71" s="139"/>
-      <c r="G71" s="139"/>
-      <c r="H71" s="139"/>
-      <c r="I71" s="139"/>
-      <c r="J71" s="139"/>
-      <c r="K71" s="139"/>
-      <c r="L71" s="139"/>
-      <c r="M71" s="139"/>
+      <c r="C71" s="116"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="116"/>
+      <c r="G71" s="116"/>
+      <c r="H71" s="116"/>
+      <c r="I71" s="116"/>
+      <c r="J71" s="116"/>
+      <c r="K71" s="116"/>
+      <c r="L71" s="116"/>
+      <c r="M71" s="116"/>
     </row>
     <row r="72" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="139" t="s">
+      <c r="B72" s="116" t="s">
         <v>621</v>
       </c>
-      <c r="C72" s="139"/>
-      <c r="D72" s="139"/>
-      <c r="E72" s="139"/>
-      <c r="F72" s="139"/>
-      <c r="G72" s="139"/>
-      <c r="H72" s="139"/>
-      <c r="I72" s="139"/>
-      <c r="J72" s="139"/>
-      <c r="K72" s="139"/>
-      <c r="L72" s="139"/>
-      <c r="M72" s="139"/>
+      <c r="C72" s="116"/>
+      <c r="D72" s="116"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="116"/>
+      <c r="G72" s="116"/>
+      <c r="H72" s="116"/>
+      <c r="I72" s="116"/>
+      <c r="J72" s="116"/>
+      <c r="K72" s="116"/>
+      <c r="L72" s="116"/>
+      <c r="M72" s="116"/>
     </row>
     <row r="73" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="139" t="s">
+      <c r="B73" s="116" t="s">
         <v>622</v>
       </c>
-      <c r="C73" s="139"/>
-      <c r="D73" s="139"/>
-      <c r="E73" s="139"/>
-      <c r="F73" s="139"/>
-      <c r="G73" s="139"/>
-      <c r="H73" s="139"/>
-      <c r="I73" s="139"/>
-      <c r="J73" s="139"/>
-      <c r="K73" s="139"/>
-      <c r="L73" s="139"/>
-      <c r="M73" s="139"/>
+      <c r="C73" s="116"/>
+      <c r="D73" s="116"/>
+      <c r="E73" s="116"/>
+      <c r="F73" s="116"/>
+      <c r="G73" s="116"/>
+      <c r="H73" s="116"/>
+      <c r="I73" s="116"/>
+      <c r="J73" s="116"/>
+      <c r="K73" s="116"/>
+      <c r="L73" s="116"/>
+      <c r="M73" s="116"/>
     </row>
     <row r="74" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
@@ -19355,43 +19355,43 @@
       <c r="B89" t="s">
         <v>637</v>
       </c>
-      <c r="D89" s="142">
+      <c r="D89" s="115">
         <f t="shared" ref="D89:M89" si="24">D75*D82</f>
         <v>0</v>
       </c>
-      <c r="E89" s="142">
+      <c r="E89" s="115">
         <f t="shared" si="24"/>
         <v>50</v>
       </c>
-      <c r="F89" s="142">
+      <c r="F89" s="115">
         <f t="shared" si="24"/>
         <v>125</v>
       </c>
-      <c r="G89" s="142">
+      <c r="G89" s="115">
         <f t="shared" si="24"/>
         <v>206.05015000000003</v>
       </c>
-      <c r="H89" s="142">
+      <c r="H89" s="115">
         <f t="shared" si="24"/>
         <v>328.29602499999999</v>
       </c>
-      <c r="I89" s="142">
+      <c r="I89" s="115">
         <f t="shared" si="24"/>
         <v>452.63901249999998</v>
       </c>
-      <c r="J89" s="142">
+      <c r="J89" s="115">
         <f t="shared" si="24"/>
         <v>565.62770624999996</v>
       </c>
-      <c r="K89" s="142">
+      <c r="K89" s="115">
         <f t="shared" si="24"/>
         <v>677.77455312500001</v>
       </c>
-      <c r="L89" s="142">
+      <c r="L89" s="115">
         <f t="shared" si="24"/>
         <v>774.05507656249995</v>
       </c>
-      <c r="M89" s="142">
+      <c r="M89" s="115">
         <f t="shared" si="24"/>
         <v>865.11598828125011</v>
       </c>
@@ -19400,43 +19400,43 @@
       <c r="B90" t="s">
         <v>638</v>
       </c>
-      <c r="D90" s="142">
+      <c r="D90" s="115">
         <f t="shared" ref="D90:M90" si="25">D76*D83</f>
         <v>105</v>
       </c>
-      <c r="E90" s="142">
+      <c r="E90" s="115">
         <f t="shared" si="25"/>
         <v>118.03749999999999</v>
       </c>
-      <c r="F90" s="142">
+      <c r="F90" s="115">
         <f t="shared" si="25"/>
         <v>252.27399999999994</v>
       </c>
-      <c r="G90" s="142">
+      <c r="G90" s="115">
         <f t="shared" si="25"/>
         <v>330.57994999999994</v>
       </c>
-      <c r="H90" s="142">
+      <c r="H90" s="115">
         <f t="shared" si="25"/>
         <v>427.71592499999991</v>
       </c>
-      <c r="I90" s="142">
+      <c r="I90" s="115">
         <f t="shared" si="25"/>
         <v>536.49066249999987</v>
       </c>
-      <c r="J90" s="142">
+      <c r="J90" s="115">
         <f t="shared" si="25"/>
         <v>596.08098124999992</v>
       </c>
-      <c r="K90" s="142">
+      <c r="K90" s="115">
         <f t="shared" si="25"/>
         <v>680.66359062499998</v>
       </c>
-      <c r="L90" s="142">
+      <c r="L90" s="115">
         <f t="shared" si="25"/>
         <v>731.1195953125</v>
       </c>
-      <c r="M90" s="142">
+      <c r="M90" s="115">
         <f t="shared" si="25"/>
         <v>760.32859765625005</v>
       </c>
@@ -19445,43 +19445,43 @@
       <c r="B91" t="s">
         <v>639</v>
       </c>
-      <c r="D91" s="142">
+      <c r="D91" s="115">
         <f t="shared" ref="D91:M91" si="26">D77*D84</f>
         <v>0</v>
       </c>
-      <c r="E91" s="142">
+      <c r="E91" s="115">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="F91" s="142">
+      <c r="F91" s="115">
         <f t="shared" si="26"/>
         <v>24.219657000000002</v>
       </c>
-      <c r="G91" s="142">
+      <c r="G91" s="115">
         <f t="shared" si="26"/>
         <v>106.54833519</v>
       </c>
-      <c r="H91" s="142">
+      <c r="H91" s="115">
         <f t="shared" si="26"/>
         <v>231.59855657730003</v>
       </c>
-      <c r="I91" s="142">
+      <c r="I91" s="115">
         <f t="shared" si="26"/>
         <v>380.95360090679105</v>
       </c>
-      <c r="J91" s="142">
+      <c r="J91" s="115">
         <f t="shared" si="26"/>
         <v>545.24509060755008</v>
       </c>
-      <c r="K91" s="142">
+      <c r="K91" s="115">
         <f t="shared" si="26"/>
         <v>707.92921970705856</v>
       </c>
-      <c r="L91" s="142">
+      <c r="L91" s="115">
         <f t="shared" si="26"/>
         <v>883.48954320372934</v>
       </c>
-      <c r="M91" s="142">
+      <c r="M91" s="115">
         <f t="shared" si="26"/>
         <v>1036.5244879464988</v>
       </c>
@@ -19490,43 +19490,43 @@
       <c r="B92" t="s">
         <v>640</v>
       </c>
-      <c r="D92" s="142">
+      <c r="D92" s="115">
         <f t="shared" ref="D92:M92" si="27">D78*D85</f>
         <v>0</v>
       </c>
-      <c r="E92" s="142">
+      <c r="E92" s="115">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="F92" s="142">
+      <c r="F92" s="115">
         <f t="shared" si="27"/>
         <v>33</v>
       </c>
-      <c r="G92" s="142">
+      <c r="G92" s="115">
         <f t="shared" si="27"/>
         <v>104.61</v>
       </c>
-      <c r="H92" s="142">
+      <c r="H92" s="115">
         <f t="shared" si="27"/>
         <v>261.95069999999998</v>
       </c>
-      <c r="I92" s="142">
+      <c r="I92" s="115">
         <f t="shared" si="27"/>
         <v>496.71540599999997</v>
       </c>
-      <c r="J92" s="142">
+      <c r="J92" s="115">
         <f t="shared" si="27"/>
         <v>725.93927802000007</v>
       </c>
-      <c r="K92" s="142">
+      <c r="K92" s="115">
         <f t="shared" si="27"/>
         <v>963.54327827340001</v>
       </c>
-      <c r="L92" s="142">
+      <c r="L92" s="115">
         <f t="shared" si="27"/>
         <v>1173.7987924431779</v>
       </c>
-      <c r="M92" s="142">
+      <c r="M92" s="115">
         <f t="shared" si="27"/>
         <v>1386.2537189369291</v>
       </c>
@@ -19535,43 +19535,43 @@
       <c r="B93" t="s">
         <v>641</v>
       </c>
-      <c r="D93" s="142">
+      <c r="D93" s="115">
         <f t="shared" ref="D93:M93" si="28">D79*D86</f>
         <v>0</v>
       </c>
-      <c r="E93" s="142">
+      <c r="E93" s="115">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="F93" s="142">
+      <c r="F93" s="115">
         <f t="shared" si="28"/>
         <v>18.952500000000001</v>
       </c>
-      <c r="G93" s="142">
+      <c r="G93" s="115">
         <f t="shared" si="28"/>
         <v>50.450874999999996</v>
       </c>
-      <c r="H93" s="142">
+      <c r="H93" s="115">
         <f t="shared" si="28"/>
         <v>100.33815625</v>
       </c>
-      <c r="I93" s="142">
+      <c r="I93" s="115">
         <f t="shared" si="28"/>
         <v>158.71214218750001</v>
       </c>
-      <c r="J93" s="142">
+      <c r="J93" s="115">
         <f t="shared" si="28"/>
         <v>225.99743164062497</v>
       </c>
-      <c r="K93" s="142">
+      <c r="K93" s="115">
         <f t="shared" si="28"/>
         <v>326.59582373046874</v>
       </c>
-      <c r="L93" s="142">
+      <c r="L93" s="115">
         <f t="shared" si="28"/>
         <v>438.56246779785153</v>
       </c>
-      <c r="M93" s="142">
+      <c r="M93" s="115">
         <f t="shared" si="28"/>
         <v>549.15185084838856</v>
       </c>
@@ -19580,43 +19580,43 @@
       <c r="B94" t="s">
         <v>642</v>
       </c>
-      <c r="D94" s="142">
+      <c r="D94" s="115">
         <f t="shared" ref="D94:M94" si="29">D80*D87</f>
         <v>0</v>
       </c>
-      <c r="E94" s="142">
+      <c r="E94" s="115">
         <f t="shared" si="29"/>
         <v>9.1199999999999992</v>
       </c>
-      <c r="F94" s="142">
+      <c r="F94" s="115">
         <f t="shared" si="29"/>
         <v>24.454249999999995</v>
       </c>
-      <c r="G94" s="142">
+      <c r="G94" s="115">
         <f t="shared" si="29"/>
         <v>50.401712499999995</v>
       </c>
-      <c r="H94" s="142">
+      <c r="H94" s="115">
         <f t="shared" si="29"/>
         <v>94.521109374999995</v>
       </c>
-      <c r="I94" s="142">
+      <c r="I94" s="115">
         <f t="shared" si="29"/>
         <v>153.07595703125</v>
       </c>
-      <c r="J94" s="142">
+      <c r="J94" s="115">
         <f t="shared" si="29"/>
         <v>224.1354177734375</v>
       </c>
-      <c r="K94" s="142">
+      <c r="K94" s="115">
         <f t="shared" si="29"/>
         <v>302.4273383300781</v>
       </c>
-      <c r="L94" s="142">
+      <c r="L94" s="115">
         <f t="shared" si="29"/>
         <v>379.4273037475586</v>
       </c>
-      <c r="M94" s="142">
+      <c r="M94" s="115">
         <f t="shared" si="29"/>
         <v>457.84277781066896</v>
       </c>
@@ -19625,43 +19625,43 @@
       <c r="B95" s="26" t="s">
         <v>643</v>
       </c>
-      <c r="D95" s="142">
+      <c r="D95" s="115">
         <f t="shared" ref="D95:M95" si="30">SUM(D89:D94)</f>
         <v>105</v>
       </c>
-      <c r="E95" s="142">
+      <c r="E95" s="115">
         <f t="shared" si="30"/>
         <v>177.1575</v>
       </c>
-      <c r="F95" s="142">
+      <c r="F95" s="115">
         <f t="shared" si="30"/>
         <v>477.90040699999992</v>
       </c>
-      <c r="G95" s="142">
+      <c r="G95" s="115">
         <f t="shared" si="30"/>
         <v>848.64102269</v>
       </c>
-      <c r="H95" s="142">
+      <c r="H95" s="115">
         <f t="shared" si="30"/>
         <v>1444.4204722022996</v>
       </c>
-      <c r="I95" s="142">
+      <c r="I95" s="115">
         <f t="shared" si="30"/>
         <v>2178.5867811255407</v>
       </c>
-      <c r="J95" s="142">
+      <c r="J95" s="115">
         <f t="shared" si="30"/>
         <v>2883.0259055416127</v>
       </c>
-      <c r="K95" s="142">
+      <c r="K95" s="115">
         <f t="shared" si="30"/>
         <v>3658.9338037910056</v>
       </c>
-      <c r="L95" s="142">
+      <c r="L95" s="115">
         <f t="shared" si="30"/>
         <v>4380.4527790673174</v>
       </c>
-      <c r="M95" s="142">
+      <c r="M95" s="115">
         <f t="shared" si="30"/>
         <v>5055.2174214799852</v>
       </c>
@@ -19698,6 +19698,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B12:M12"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B28:M28"/>
+    <mergeCell ref="B37:M37"/>
+    <mergeCell ref="B42:M42"/>
+    <mergeCell ref="B51:M51"/>
+    <mergeCell ref="B59:M59"/>
     <mergeCell ref="B71:M71"/>
     <mergeCell ref="B72:M72"/>
     <mergeCell ref="B73:M73"/>
@@ -19706,16 +19716,6 @@
     <mergeCell ref="B68:M68"/>
     <mergeCell ref="B69:M69"/>
     <mergeCell ref="B70:M70"/>
-    <mergeCell ref="B28:M28"/>
-    <mergeCell ref="B37:M37"/>
-    <mergeCell ref="B42:M42"/>
-    <mergeCell ref="B51:M51"/>
-    <mergeCell ref="B59:M59"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B12:M12"/>
-    <mergeCell ref="B19:M19"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -19738,21 +19738,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -19793,21 +19793,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>653</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
@@ -20922,21 +20922,21 @@
       </c>
     </row>
     <row r="36" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="118" t="s">
+      <c r="B36" s="117" t="s">
         <v>682</v>
       </c>
-      <c r="C36" s="118"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="118"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="118"/>
-      <c r="L36" s="118"/>
-      <c r="M36" s="118"/>
-      <c r="N36" s="118"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="117"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="117"/>
+      <c r="G36" s="117"/>
+      <c r="H36" s="117"/>
+      <c r="I36" s="117"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="117"/>
+      <c r="L36" s="117"/>
+      <c r="M36" s="117"/>
+      <c r="N36" s="117"/>
     </row>
     <row r="37" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="68" t="s">
@@ -22283,20 +22283,20 @@
       </c>
     </row>
     <row r="66" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="118" t="s">
+      <c r="B66" s="117" t="s">
         <v>715</v>
       </c>
-      <c r="C66" s="118"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="118"/>
-      <c r="G66" s="118"/>
-      <c r="H66" s="118"/>
-      <c r="I66" s="118"/>
-      <c r="J66" s="118"/>
-      <c r="K66" s="118"/>
-      <c r="L66" s="118"/>
-      <c r="M66" s="118"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="117"/>
+      <c r="E66" s="117"/>
+      <c r="F66" s="117"/>
+      <c r="G66" s="117"/>
+      <c r="H66" s="117"/>
+      <c r="I66" s="117"/>
+      <c r="J66" s="117"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="117"/>
+      <c r="M66" s="117"/>
     </row>
     <row r="67" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="42" t="s">
@@ -22532,20 +22532,20 @@
       </c>
     </row>
     <row r="72" spans="2:13" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="140" t="s">
+      <c r="B72" s="141" t="s">
         <v>721</v>
       </c>
-      <c r="C72" s="140"/>
-      <c r="D72" s="140"/>
-      <c r="E72" s="140"/>
-      <c r="F72" s="140"/>
-      <c r="G72" s="140"/>
-      <c r="H72" s="140"/>
-      <c r="I72" s="140"/>
-      <c r="J72" s="140"/>
-      <c r="K72" s="140"/>
-      <c r="L72" s="140"/>
-      <c r="M72" s="140"/>
+      <c r="C72" s="141"/>
+      <c r="D72" s="141"/>
+      <c r="E72" s="141"/>
+      <c r="F72" s="141"/>
+      <c r="G72" s="141"/>
+      <c r="H72" s="141"/>
+      <c r="I72" s="141"/>
+      <c r="J72" s="141"/>
+      <c r="K72" s="141"/>
+      <c r="L72" s="141"/>
+      <c r="M72" s="141"/>
     </row>
     <row r="76" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="91" t="s">
@@ -22582,21 +22582,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>723</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -22874,21 +22874,21 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
     </row>
     <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="58" t="s">
@@ -23213,41 +23213,41 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="119" t="s">
+      <c r="B2" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
+      <c r="I2" s="126"/>
+      <c r="J2" s="126"/>
+      <c r="K2" s="126"/>
+      <c r="L2" s="126"/>
     </row>
     <row r="3" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="120" t="s">
+      <c r="B3" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="120" t="s">
+      <c r="C3" s="127"/>
+      <c r="D3" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="120"/>
-      <c r="F3" s="120" t="s">
+      <c r="E3" s="127"/>
+      <c r="F3" s="127" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="120"/>
-      <c r="H3" s="120" t="s">
+      <c r="G3" s="127"/>
+      <c r="H3" s="127" t="s">
         <v>54</v>
       </c>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120" t="s">
+      <c r="I3" s="127"/>
+      <c r="J3" s="127" t="s">
         <v>55</v>
       </c>
-      <c r="K3" s="120"/>
+      <c r="K3" s="127"/>
     </row>
     <row r="4" spans="2:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="123">
@@ -23277,20 +23277,20 @@
       <c r="K4" s="123"/>
     </row>
     <row r="6" spans="2:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="121"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="121"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="121"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="121"/>
-      <c r="M6" s="121"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
+      <c r="L6" s="118"/>
+      <c r="M6" s="118"/>
     </row>
     <row r="8" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
@@ -24453,20 +24453,20 @@
       </c>
     </row>
     <row r="35" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="118" t="s">
+      <c r="B35" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="C35" s="118"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="118"/>
-      <c r="K35" s="118"/>
-      <c r="L35" s="118"/>
-      <c r="M35" s="118"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="117"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="117"/>
+      <c r="G35" s="117"/>
+      <c r="H35" s="117"/>
+      <c r="I35" s="117"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="117"/>
+      <c r="L35" s="117"/>
+      <c r="M35" s="117"/>
     </row>
     <row r="36" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="12" t="s">
@@ -24904,6 +24904,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
     <mergeCell ref="B6:M6"/>
     <mergeCell ref="B35:M35"/>
     <mergeCell ref="B49:M49"/>
@@ -24912,12 +24918,6 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B2:L2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -24941,21 +24941,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>747</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -24996,21 +24996,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>750</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
@@ -25606,21 +25606,21 @@
       </c>
     </row>
     <row r="23" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="118" t="s">
+      <c r="B23" s="117" t="s">
         <v>767</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="118"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="118"/>
-      <c r="I23" s="118"/>
-      <c r="J23" s="118"/>
-      <c r="K23" s="118"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="118"/>
-      <c r="N23" s="118"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="117"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="117"/>
+      <c r="M23" s="117"/>
+      <c r="N23" s="117"/>
     </row>
     <row r="24" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="71" t="s">
@@ -26369,21 +26369,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>784</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -26421,21 +26421,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>785</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
@@ -27142,20 +27142,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>804</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -28720,20 +28720,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>834</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -28771,20 +28771,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>835</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -29237,20 +29237,20 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>845</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="118"/>
-      <c r="J16" s="118"/>
-      <c r="K16" s="118"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="118"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
+      <c r="H16" s="117"/>
+      <c r="I16" s="117"/>
+      <c r="J16" s="117"/>
+      <c r="K16" s="117"/>
+      <c r="L16" s="117"/>
+      <c r="M16" s="117"/>
     </row>
     <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
@@ -29388,20 +29388,20 @@
       </c>
     </row>
     <row r="21" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="118" t="s">
+      <c r="B21" s="117" t="s">
         <v>849</v>
       </c>
-      <c r="C21" s="118"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="118"/>
-      <c r="G21" s="118"/>
-      <c r="H21" s="118"/>
-      <c r="I21" s="118"/>
-      <c r="J21" s="118"/>
-      <c r="K21" s="118"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="117"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
+      <c r="G21" s="117"/>
+      <c r="H21" s="117"/>
+      <c r="I21" s="117"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="117"/>
+      <c r="L21" s="117"/>
+      <c r="M21" s="117"/>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="43" t="s">
@@ -29539,20 +29539,20 @@
       </c>
     </row>
     <row r="26" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="118" t="s">
+      <c r="B26" s="117" t="s">
         <v>852</v>
       </c>
-      <c r="C26" s="118"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="118"/>
-      <c r="G26" s="118"/>
-      <c r="H26" s="118"/>
-      <c r="I26" s="118"/>
-      <c r="J26" s="118"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="118"/>
-      <c r="M26" s="118"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="117"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
+      <c r="G26" s="117"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="117"/>
+      <c r="L26" s="117"/>
+      <c r="M26" s="117"/>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
@@ -29988,36 +29988,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>862</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="3" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="116" t="s">
         <v>863</v>
       </c>
-      <c r="C3" s="139"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="139"/>
-      <c r="F3" s="139"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="139"/>
-      <c r="K3" s="139"/>
-      <c r="L3" s="139"/>
-      <c r="M3" s="139"/>
+      <c r="C3" s="116"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="116"/>
+      <c r="F3" s="116"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="116"/>
+      <c r="K3" s="116"/>
+      <c r="L3" s="116"/>
+      <c r="M3" s="116"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -30055,20 +30055,20 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>864</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
     </row>
     <row r="6" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -30566,20 +30566,20 @@
       </c>
     </row>
     <row r="18" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="117" t="s">
         <v>875</v>
       </c>
-      <c r="C18" s="118"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="118"/>
-      <c r="H18" s="118"/>
-      <c r="I18" s="118"/>
-      <c r="J18" s="118"/>
-      <c r="K18" s="118"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="117"/>
+      <c r="H18" s="117"/>
+      <c r="I18" s="117"/>
+      <c r="J18" s="117"/>
+      <c r="K18" s="117"/>
+      <c r="L18" s="117"/>
+      <c r="M18" s="117"/>
     </row>
     <row r="19" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
@@ -30762,20 +30762,20 @@
       </c>
     </row>
     <row r="24" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="118" t="s">
+      <c r="B24" s="117" t="s">
         <v>880</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="118"/>
-      <c r="H24" s="118"/>
-      <c r="I24" s="118"/>
-      <c r="J24" s="118"/>
-      <c r="K24" s="118"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="118"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="117"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="117"/>
+      <c r="L24" s="117"/>
+      <c r="M24" s="117"/>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
@@ -30958,20 +30958,20 @@
       </c>
     </row>
     <row r="31" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="118" t="s">
+      <c r="B31" s="117" t="s">
         <v>885</v>
       </c>
-      <c r="C31" s="118"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="118"/>
-      <c r="J31" s="118"/>
-      <c r="K31" s="118"/>
-      <c r="L31" s="118"/>
-      <c r="M31" s="118"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="117"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="117"/>
+      <c r="G31" s="117"/>
+      <c r="H31" s="117"/>
+      <c r="I31" s="117"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="117"/>
+      <c r="L31" s="117"/>
+      <c r="M31" s="117"/>
     </row>
     <row r="32" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
@@ -31408,21 +31408,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>895</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -31463,21 +31463,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>898</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="12" t="s">
@@ -31677,21 +31677,21 @@
       </c>
     </row>
     <row r="11" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="117" t="s">
         <v>907</v>
       </c>
-      <c r="C11" s="118"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="118"/>
-      <c r="G11" s="118"/>
-      <c r="H11" s="118"/>
-      <c r="I11" s="118"/>
-      <c r="J11" s="118"/>
-      <c r="K11" s="118"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
     </row>
     <row r="12" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
@@ -31946,21 +31946,21 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="117" t="s">
         <v>914</v>
       </c>
-      <c r="C19" s="118"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="118"/>
-      <c r="G19" s="118"/>
-      <c r="H19" s="118"/>
-      <c r="I19" s="118"/>
-      <c r="J19" s="118"/>
-      <c r="K19" s="118"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="117"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
+      <c r="G19" s="117"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="117"/>
+      <c r="J19" s="117"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="117"/>
+      <c r="M19" s="117"/>
+      <c r="N19" s="117"/>
     </row>
     <row r="20" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="43" t="s">
@@ -32280,14 +32280,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="142" t="s">
         <v>924</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
     </row>
     <row r="4" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
@@ -32298,14 +32298,14 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="117" t="s">
         <v>926</v>
       </c>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="118"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
     </row>
     <row r="7" spans="2:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
@@ -32508,14 +32508,14 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>934</v>
       </c>
-      <c r="C16" s="118"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="117"/>
     </row>
     <row r="17" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -32581,14 +32581,14 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="118" t="s">
+      <c r="B25" s="117" t="s">
         <v>942</v>
       </c>
-      <c r="C25" s="118"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="118"/>
-      <c r="G25" s="118"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
     </row>
     <row r="26" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="43" t="s">
@@ -32609,14 +32609,14 @@
       </c>
     </row>
     <row r="29" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="118" t="s">
+      <c r="B29" s="117" t="s">
         <v>945</v>
       </c>
-      <c r="C29" s="118"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="117"/>
+      <c r="G29" s="117"/>
     </row>
     <row r="30" spans="2:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
@@ -32745,10 +32745,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="121"/>
+      <c r="C2" s="118"/>
     </row>
     <row r="4" spans="2:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -32862,16 +32862,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
     </row>
     <row r="4" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -33323,72 +33323,72 @@
       </c>
     </row>
     <row r="22" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
     </row>
     <row r="23" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="117" t="s">
+      <c r="C23" s="119" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
     </row>
     <row r="24" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="117" t="s">
+      <c r="C24" s="119" t="s">
         <v>170</v>
       </c>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
     </row>
     <row r="25" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="117" t="s">
+      <c r="C25" s="119" t="s">
         <v>172</v>
       </c>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
     </row>
     <row r="26" spans="2:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C26" s="117" t="s">
+      <c r="C26" s="119" t="s">
         <v>174</v>
       </c>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="F26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="119"/>
+      <c r="H26" s="119"/>
+      <c r="I26" s="119"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -33432,20 +33432,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
     </row>
     <row r="4" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -34008,20 +34008,20 @@
       </c>
     </row>
     <row r="20" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="117"/>
     </row>
     <row r="21" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="39" t="s">
@@ -34081,21 +34081,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
@@ -34136,21 +34136,21 @@
       </c>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="118" t="s">
+      <c r="B5" s="117" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
     </row>
     <row r="6" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -34436,21 +34436,21 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>233</v>
       </c>
-      <c r="C14" s="118"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="118"/>
-      <c r="J14" s="118"/>
-      <c r="K14" s="118"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="117"/>
+      <c r="H14" s="117"/>
+      <c r="I14" s="117"/>
+      <c r="J14" s="117"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="117"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="117"/>
     </row>
     <row r="15" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
@@ -34643,21 +34643,21 @@
       </c>
     </row>
     <row r="20" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="117" t="s">
         <v>235</v>
       </c>
-      <c r="C20" s="118"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="118"/>
-      <c r="G20" s="118"/>
-      <c r="H20" s="118"/>
-      <c r="I20" s="118"/>
-      <c r="J20" s="118"/>
-      <c r="K20" s="118"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="117"/>
+      <c r="H20" s="117"/>
+      <c r="I20" s="117"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="117"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
     </row>
     <row r="21" spans="2:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="43" t="s">
@@ -34910,38 +34910,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="B2" s="126" t="s">
+      <c r="B2" s="130" t="s">
         <v>241</v>
       </c>
-      <c r="C2" s="126"/>
-      <c r="D2" s="126"/>
-      <c r="E2" s="126"/>
-      <c r="F2" s="126"/>
-      <c r="G2" s="126"/>
-      <c r="H2" s="126"/>
-      <c r="I2" s="126"/>
-      <c r="J2" s="126"/>
-      <c r="K2" s="126"/>
-      <c r="L2" s="126"/>
-      <c r="M2" s="126"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="106" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="127" t="s">
+      <c r="C3" s="129" t="s">
         <v>243</v>
       </c>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="127"/>
-      <c r="I3" s="127"/>
-      <c r="J3" s="127"/>
-      <c r="K3" s="127"/>
-      <c r="L3" s="127"/>
-      <c r="M3" s="127"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
+      <c r="I3" s="129"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="129"/>
+      <c r="M3" s="129"/>
     </row>
     <row r="5" spans="2:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="128" t="s">
@@ -38074,22 +38074,27 @@
       <c r="B104" s="106" t="s">
         <v>299</v>
       </c>
-      <c r="C104" s="127" t="s">
+      <c r="C104" s="129" t="s">
         <v>300</v>
       </c>
-      <c r="D104" s="127"/>
-      <c r="E104" s="127"/>
-      <c r="F104" s="127"/>
-      <c r="G104" s="127"/>
-      <c r="H104" s="127"/>
-      <c r="I104" s="127"/>
-      <c r="J104" s="127"/>
-      <c r="K104" s="127"/>
-      <c r="L104" s="127"/>
-      <c r="M104" s="127"/>
+      <c r="D104" s="129"/>
+      <c r="E104" s="129"/>
+      <c r="F104" s="129"/>
+      <c r="G104" s="129"/>
+      <c r="H104" s="129"/>
+      <c r="I104" s="129"/>
+      <c r="J104" s="129"/>
+      <c r="K104" s="129"/>
+      <c r="L104" s="129"/>
+      <c r="M104" s="129"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="C3:M3"/>
+    <mergeCell ref="B5:M5"/>
+    <mergeCell ref="B14:M14"/>
+    <mergeCell ref="B23:M23"/>
     <mergeCell ref="B85:M85"/>
     <mergeCell ref="B97:M97"/>
     <mergeCell ref="C104:M104"/>
@@ -38098,11 +38103,6 @@
     <mergeCell ref="B52:M52"/>
     <mergeCell ref="B63:M63"/>
     <mergeCell ref="B74:M74"/>
-    <mergeCell ref="B2:M2"/>
-    <mergeCell ref="C3:M3"/>
-    <mergeCell ref="B5:M5"/>
-    <mergeCell ref="B14:M14"/>
-    <mergeCell ref="B23:M23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -38124,38 +38124,38 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="121" t="s">
+      <c r="B2" s="118" t="s">
         <v>301</v>
       </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="121"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="121"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="121"/>
-      <c r="N2" s="121"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="118"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="129" t="s">
+      <c r="B4" s="135" t="s">
         <v>302</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="129"/>
-      <c r="K4" s="129"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="129"/>
-      <c r="N4" s="129"/>
+      <c r="C4" s="135"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="135"/>
+      <c r="J4" s="135"/>
+      <c r="K4" s="135"/>
+      <c r="L4" s="135"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
     </row>
     <row r="5" spans="2:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
@@ -38325,21 +38325,21 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="117" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="118"/>
-      <c r="G13" s="118"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="118"/>
-      <c r="J13" s="118"/>
-      <c r="K13" s="118"/>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117"/>
+      <c r="I13" s="117"/>
+      <c r="J13" s="117"/>
+      <c r="K13" s="117"/>
+      <c r="L13" s="117"/>
+      <c r="M13" s="117"/>
+      <c r="N13" s="117"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
@@ -38648,21 +38648,21 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="117" t="s">
         <v>316</v>
       </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="118"/>
-      <c r="H22" s="118"/>
-      <c r="I22" s="118"/>
-      <c r="J22" s="118"/>
-      <c r="K22" s="118"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="117"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
+      <c r="G22" s="117"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="117"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="117"/>
+      <c r="L22" s="117"/>
+      <c r="M22" s="117"/>
+      <c r="N22" s="117"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
@@ -39507,27 +39507,27 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="118" t="s">
+      <c r="B43" s="117" t="s">
         <v>345</v>
       </c>
-      <c r="C43" s="118"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="118"/>
-      <c r="G43" s="118"/>
-      <c r="H43" s="118"/>
-      <c r="I43" s="118"/>
-      <c r="J43" s="118"/>
-      <c r="K43" s="118"/>
-      <c r="L43" s="118"/>
-      <c r="M43" s="118"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="117"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="117"/>
+      <c r="G43" s="117"/>
+      <c r="H43" s="117"/>
+      <c r="I43" s="117"/>
+      <c r="J43" s="117"/>
+      <c r="K43" s="117"/>
+      <c r="L43" s="117"/>
+      <c r="M43" s="117"/>
       <c r="N43" s="57"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="131" t="s">
+      <c r="B44" s="132" t="s">
         <v>346</v>
       </c>
-      <c r="C44" s="131"/>
+      <c r="C44" s="132"/>
       <c r="D44" s="11" t="s">
         <v>30</v>
       </c>
@@ -39560,10 +39560,10 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="132" t="s">
+      <c r="B45" s="133" t="s">
         <v>347</v>
       </c>
-      <c r="C45" s="132"/>
+      <c r="C45" s="133"/>
       <c r="D45" s="44">
         <f t="shared" ref="D45:M45" si="13">D24+D27+D30+D33+D36+D39</f>
         <v>261.72500000000002</v>
@@ -39606,10 +39606,10 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="132" t="s">
+      <c r="B46" s="133" t="s">
         <v>348</v>
       </c>
-      <c r="C46" s="132"/>
+      <c r="C46" s="133"/>
       <c r="D46" s="44">
         <f t="shared" ref="D46:M46" si="14">D25+D28+D31+D34+D37+D40</f>
         <v>141.82787500000001</v>
@@ -39652,10 +39652,10 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B47" s="133" t="s">
+      <c r="B47" s="134" t="s">
         <v>349</v>
       </c>
-      <c r="C47" s="133"/>
+      <c r="C47" s="134"/>
       <c r="D47" s="44">
         <f t="shared" ref="D47:M47" si="15">D45-D46</f>
         <v>119.89712500000002</v>
@@ -39698,10 +39698,10 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B48" s="132" t="s">
+      <c r="B48" s="133" t="s">
         <v>350</v>
       </c>
-      <c r="C48" s="132"/>
+      <c r="C48" s="133"/>
       <c r="D48" s="44">
         <f>Platform!D11</f>
         <v>101</v>
@@ -39744,10 +39744,10 @@
       </c>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B49" s="130" t="s">
+      <c r="B49" s="131" t="s">
         <v>351</v>
       </c>
-      <c r="C49" s="130"/>
+      <c r="C49" s="131"/>
       <c r="D49" s="59">
         <f t="shared" ref="D49:M49" si="16">D46+D48</f>
         <v>242.82787500000001</v>
@@ -39791,17 +39791,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="B4:N4"/>
+    <mergeCell ref="B13:N13"/>
+    <mergeCell ref="B22:N22"/>
+    <mergeCell ref="B43:M43"/>
     <mergeCell ref="B49:C49"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="B46:C46"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B2:N2"/>
-    <mergeCell ref="B4:N4"/>
-    <mergeCell ref="B13:N13"/>
-    <mergeCell ref="B22:N22"/>
-    <mergeCell ref="B43:M43"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -40094,11 +40094,11 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="117" t="s">
         <v>400</v>
       </c>
-      <c r="C28" s="118"/>
-      <c r="D28" s="118"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="117"/>
     </row>
     <row r="29" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A29" s="46" t="s">
@@ -40107,10 +40107,10 @@
       <c r="B29" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="C29" s="117">
+      <c r="C29" s="119">
         <v>0.5</v>
       </c>
-      <c r="D29" s="117"/>
+      <c r="D29" s="119"/>
     </row>
     <row r="30" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" s="46" t="s">
@@ -40119,64 +40119,64 @@
       <c r="B30" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C30" s="117">
+      <c r="C30" s="119">
         <v>0.7</v>
       </c>
-      <c r="D30" s="117"/>
+      <c r="D30" s="119"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C31" s="117" t="s">
+      <c r="C31" s="119" t="s">
         <v>406</v>
       </c>
-      <c r="D31" s="117"/>
+      <c r="D31" s="119"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C32" s="117" t="s">
+      <c r="C32" s="119" t="s">
         <v>408</v>
       </c>
-      <c r="D32" s="117"/>
+      <c r="D32" s="119"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C33" s="117" t="s">
+      <c r="C33" s="119" t="s">
         <v>410</v>
       </c>
-      <c r="D33" s="117"/>
+      <c r="D33" s="119"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C34" s="117" t="s">
+      <c r="C34" s="119" t="s">
         <v>412</v>
       </c>
-      <c r="D34" s="117"/>
+      <c r="D34" s="119"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C35" s="117" t="s">
+      <c r="C35" s="119" t="s">
         <v>414</v>
       </c>
-      <c r="D35" s="117"/>
+      <c r="D35" s="119"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C36" s="117" t="s">
+      <c r="C36" s="119" t="s">
         <v>416</v>
       </c>
-      <c r="D36" s="117"/>
+      <c r="D36" s="119"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
